--- a/figures/FMNIST/tables/learning_rate/noise_fashion_v2_delta_fashion_v1/results.xlsx
+++ b/figures/FMNIST/tables/learning_rate/noise_fashion_v2_delta_fashion_v1/results.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maciek\Documents\GitHub\MUNDataStream\figures\FMNIST\tables\learning_rate\noise_fashion_v2_delta_fashion_v1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B5F4B7-59E7-4537-BF45-12EF2346093E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="4650" yWindow="5730" windowWidth="28800" windowHeight="15885" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="accuracy" sheetId="1" r:id="rId1"/>
     <sheet name="recovery_time" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>learning_rate</t>
   </si>
@@ -35,17 +41,14 @@
     <t>accuracy_recovery_time</t>
   </si>
   <si>
-    <t>mean_memory</t>
-  </si>
-  <si>
     <t>mean_time</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,17 +107,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Pakiet Office 2007–2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -152,7 +163,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Pakiet Office 2007–2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -186,6 +197,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -220,9 +232,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Pakiet Office 2007–2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,11 +408,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -413,88 +426,88 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.8585721107927411</v>
+        <v>0.85857211079274109</v>
       </c>
       <c r="C2">
-        <v>0.9222222222222222</v>
+        <v>0.92222222222222217</v>
       </c>
       <c r="D2">
-        <v>0.7952857142857144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>0.79528571428571437</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.8598615090735435</v>
+        <v>0.85986150907354353</v>
       </c>
       <c r="C3">
-        <v>0.9266666666666666</v>
+        <v>0.92666666666666664</v>
       </c>
       <c r="D3">
-        <v>0.7934380952380953</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>0.79343809523809528</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.04</v>
       </c>
       <c r="B4">
-        <v>0.8535339063992359</v>
+        <v>0.85353390639923588</v>
       </c>
       <c r="C4">
-        <v>0.9301149425287356</v>
+        <v>0.93011494252873561</v>
       </c>
       <c r="D4">
-        <v>0.7773904761904762</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>0.77739047619047619</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.08</v>
       </c>
       <c r="B5">
-        <v>0.7545176695319962</v>
+        <v>0.75451766953199617</v>
       </c>
       <c r="C5">
-        <v>0.8397318007662836</v>
+        <v>0.83973180076628362</v>
       </c>
       <c r="D5">
-        <v>0.6697904761904762</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>0.66979047619047616</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.16</v>
       </c>
       <c r="B6">
-        <v>0.597655205348615</v>
+        <v>0.59765520534861505</v>
       </c>
       <c r="C6">
-        <v>0.6950766283524905</v>
+        <v>0.69507662835249051</v>
       </c>
       <c r="D6">
-        <v>0.5007904761904761</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>0.50079047619047612</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7">
-        <v>0.8698376313276027</v>
+        <v>0.86983763132760272</v>
       </c>
       <c r="C7">
-        <v>0.9212452107279693</v>
+        <v>0.92124521072796928</v>
       </c>
       <c r="D7">
-        <v>0.8187238095238096</v>
+        <v>0.81872380952380963</v>
       </c>
     </row>
   </sheetData>
@@ -503,11 +516,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,11 +530,8 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0.01</v>
       </c>
@@ -529,41 +539,32 @@
         <v>47</v>
       </c>
       <c r="C2">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D2">
-        <v>3.600064684100311</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>3.6000646841003112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0.02</v>
       </c>
       <c r="B3">
-        <v>50.33333333333334</v>
+        <v>50.333333333333343</v>
       </c>
       <c r="C3">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D3">
-        <v>3.595250215671398</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>3.5952502156713981</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0.04</v>
       </c>
       <c r="B4">
-        <v>70.33333333333333</v>
+        <v>70.333333333333329</v>
       </c>
       <c r="C4">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D4">
-        <v>3.594101357537738</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>3.5941013575377379</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0.08</v>
       </c>
@@ -571,24 +572,18 @@
         <v>60.5</v>
       </c>
       <c r="C5">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D5">
-        <v>3.592803495906402</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>3.5928034959064021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0.16</v>
       </c>
       <c r="C6">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D6">
-        <v>3.592762585818525</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>3.5927625858185248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -596,10 +591,7 @@
         <v>13.33333333333333</v>
       </c>
       <c r="C7">
-        <v>8033865.902578796</v>
-      </c>
-      <c r="D7">
-        <v>6.258527898987587</v>
+        <v>6.2585278989875874</v>
       </c>
     </row>
   </sheetData>
